--- a/Tables/AAR_tech.xlsx
+++ b/Tables/AAR_tech.xlsx
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.647689828960999</v>
+        <v>-0.9243123562538248</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.230369669246582</v>
+        <v>-1.294013909576714</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1915470340685752</v>
+        <v>0.04650851038143084</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.196582582730806</v>
+        <v>-2.131543528374097</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.307460835427874</v>
+        <v>-2.52236866808602</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5048301122175085</v>
+        <v>0.2217319995232427</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7084960899670161</v>
+        <v>0.5394031237211865</v>
       </c>
     </row>
     <row r="4">
@@ -514,25 +514,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1333086261009617</v>
+        <v>0.008591641012074788</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.7873831685061827</v>
+        <v>-0.5425188100803361</v>
       </c>
       <c r="D4" t="n">
-        <v>1.593589439309117</v>
+        <v>2.30700437473446</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.309924833002778</v>
+        <v>-0.7916625764218528</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.843689807089026</v>
+        <v>-1.6497815384982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8747631431777313</v>
+        <v>1.092271365905511</v>
       </c>
       <c r="H4" t="n">
-        <v>1.048388520773323</v>
+        <v>1.260508468681782</v>
       </c>
     </row>
   </sheetData>

--- a/Tables/AAR_tech.xlsx
+++ b/Tables/AAR_tech.xlsx
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9243123562538248</v>
+        <v>-0.926701957487311</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.294013909576714</v>
+        <v>-1.288664656842581</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04650851038143084</v>
+        <v>0.009755540513534989</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.131543528374097</v>
+        <v>-2.12284468615509</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.52236866808602</v>
+        <v>-2.533220659740076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2217319995232427</v>
+        <v>0.2380283199933569</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5394031237211865</v>
+        <v>0.5415521820136689</v>
       </c>
     </row>
     <row r="4">
@@ -514,25 +514,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008591641012074788</v>
+        <v>0.004545243366515536</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5425188100803361</v>
+        <v>-0.5315179915836284</v>
       </c>
       <c r="D4" t="n">
-        <v>2.30700437473446</v>
+        <v>2.280907786733563</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7916625764218528</v>
+        <v>-0.8002784960487515</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6497815384982</v>
+        <v>-1.645490378118673</v>
       </c>
       <c r="G4" t="n">
-        <v>1.092271365905511</v>
+        <v>1.092539330302742</v>
       </c>
       <c r="H4" t="n">
-        <v>1.260508468681782</v>
+        <v>1.255866932505461</v>
       </c>
     </row>
   </sheetData>
